--- a/data/trans_orig/IP04D$aparatos-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$aparatos-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79704</t>
+          <t>79591</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98991</t>
+          <t>98113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69664</t>
+          <t>69120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88244</t>
+          <t>89704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154292</t>
+          <t>154641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181961</t>
+          <t>181693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45462</t>
+          <t>46340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64749</t>
+          <t>64862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57118</t>
+          <t>55658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75698</t>
+          <t>76242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107853</t>
+          <t>108121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135522</t>
+          <t>135173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146330</t>
+          <t>145989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169890</t>
+          <t>169648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162902</t>
+          <t>163915</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189288</t>
+          <t>191024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>315817</t>
+          <t>316411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>351678</t>
+          <t>352092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>66602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>90261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79049</t>
+          <t>77313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105435</t>
+          <t>104422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152909</t>
+          <t>152495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188770</t>
+          <t>188176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89806</t>
+          <t>90085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109155</t>
+          <t>110108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82360</t>
+          <t>82604</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103793</t>
+          <t>103156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177051</t>
+          <t>177438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206277</t>
+          <t>205899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>46145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66447</t>
+          <t>66168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54778</t>
+          <t>55415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76211</t>
+          <t>75967</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108547</t>
+          <t>108925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137773</t>
+          <t>137386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98912</t>
+          <t>100342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120461</t>
+          <t>121531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105527</t>
+          <t>105471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126060</t>
+          <t>126590</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210782</t>
+          <t>210780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241637</t>
+          <t>240168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,37%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50876</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72425</t>
+          <t>70995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53895</t>
+          <t>53365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74428</t>
+          <t>74484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109655</t>
+          <t>111124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140510</t>
+          <t>140512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>435016</t>
+          <t>433746</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>476483</t>
+          <t>477138</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>442269</t>
+          <t>444078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>486898</t>
+          <t>487362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>890540</t>
+          <t>890450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>951405</t>
+          <t>953410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>231809</t>
+          <t>231154</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273276</t>
+          <t>274546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>265327</t>
+          <t>264863</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>309956</t>
+          <t>308147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>509112</t>
+          <t>507107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569977</t>
+          <t>570067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65312</t>
+          <t>65813</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83928</t>
+          <t>83541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59417</t>
+          <t>59141</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76796</t>
+          <t>77112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129166</t>
+          <t>129635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154052</t>
+          <t>155284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47726</t>
+          <t>48113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66342</t>
+          <t>65841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47368</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64747</t>
+          <t>65023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101766</t>
+          <t>100534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126652</t>
+          <t>126183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88841</t>
+          <t>88051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111730</t>
+          <t>112164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>124153</t>
+          <t>122775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148690</t>
+          <t>148933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>220407</t>
+          <t>219207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>255763</t>
+          <t>254661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,82%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96718</t>
+          <t>96284</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119607</t>
+          <t>120397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107394</t>
+          <t>107151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>131931</t>
+          <t>133309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208769</t>
+          <t>209871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>244125</t>
+          <t>245325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87840</t>
+          <t>88716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110522</t>
+          <t>111403</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82715</t>
+          <t>83325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105674</t>
+          <t>105210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177660</t>
+          <t>179502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210805</t>
+          <t>209569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76918</t>
+          <t>76037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99600</t>
+          <t>98724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80713</t>
+          <t>81177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103672</t>
+          <t>103062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163022</t>
+          <t>164258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196167</t>
+          <t>194325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76419</t>
+          <t>76470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98890</t>
+          <t>98232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78200</t>
+          <t>80577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101396</t>
+          <t>102749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162171</t>
+          <t>162271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194354</t>
+          <t>193877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73748</t>
+          <t>74406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96219</t>
+          <t>96168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71981</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95177</t>
+          <t>92800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151661</t>
+          <t>152138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183844</t>
+          <t>183744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>341465</t>
+          <t>340584</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382945</t>
+          <t>383439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>367598</t>
+          <t>366690</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>413510</t>
+          <t>411755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>720906</t>
+          <t>722137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>781491</t>
+          <t>784270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>317236</t>
+          <t>316742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>358716</t>
+          <t>359597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326501</t>
+          <t>328256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>372413</t>
+          <t>373321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>658701</t>
+          <t>655922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>719286</t>
+          <t>718055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>27555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39119</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30983</t>
+          <t>30940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42370</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62514</t>
+          <t>63154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78290</t>
+          <t>79425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29569</t>
+          <t>29956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30461</t>
+          <t>30504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40665</t>
+          <t>39530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56441</t>
+          <t>55801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86565</t>
+          <t>86057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106684</t>
+          <t>107172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108895</t>
+          <t>109306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130543</t>
+          <t>131387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201065</t>
+          <t>201832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>231360</t>
+          <t>232299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52615</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72734</t>
+          <t>73242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51304</t>
+          <t>50460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72952</t>
+          <t>72541</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109787</t>
+          <t>108848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140082</t>
+          <t>139315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>104136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126740</t>
+          <t>125461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96994</t>
+          <t>96240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126005</t>
+          <t>125285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>208980</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244536</t>
+          <t>245684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>48427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69295</t>
+          <t>69752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85542</t>
+          <t>86262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114553</t>
+          <t>115307</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>139750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176454</t>
+          <t>178342</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149928</t>
+          <t>150693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201912</t>
+          <t>201725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152003</t>
+          <t>151679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197304</t>
+          <t>195979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>313564</t>
+          <t>318152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>382472</t>
+          <t>389379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72546</t>
+          <t>72733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124530</t>
+          <t>123765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108179</t>
+          <t>109504</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153480</t>
+          <t>153804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>197469</t>
+          <t>190562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>266377</t>
+          <t>261789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>390190</t>
+          <t>391941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>449372</t>
+          <t>454634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>413919</t>
+          <t>411370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>476641</t>
+          <t>473302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>820184</t>
+          <t>822563</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>907555</t>
+          <t>903394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>215784</t>
+          <t>210522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>274966</t>
+          <t>273215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>283681</t>
+          <t>287020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>346403</t>
+          <t>348952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>517922</t>
+          <t>522083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>605293</t>
+          <t>602914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$aparatos-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$aparatos-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>79228</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69981</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>90136</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>48,14%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,01%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>88852</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>79591</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>98113</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>78625</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>97395</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>55,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>79228</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>69120</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>89704</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>54,5%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154641</t>
+          <t>154536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181693</t>
+          <t>182588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66134</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55226</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75381</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55601</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46340</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64862</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47058</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>65828</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66134</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55658</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>76242</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>45,5%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108121</t>
+          <t>107226</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135173</t>
+          <t>135278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145362</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>144453</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>176810</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>163160</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>189869</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>65,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>157805</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>145989</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>169648</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>144950</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>169044</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>66,8%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>176810</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>163915</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>191024</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>65,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>316411</t>
+          <t>316808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>352092</t>
+          <t>351620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,68%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91527</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78468</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>105177</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>34,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,24%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>78445</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>66602</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>90261</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>67206</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>91300</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>33,2%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>91527</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>77313</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>104422</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>34,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152495</t>
+          <t>152967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188176</t>
+          <t>187779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268337</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93195</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>82816</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>103491</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>99278</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>90085</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>110108</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>89500</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>109039</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>93195</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>82604</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>103156</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177438</t>
+          <t>177475</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205899</t>
+          <t>206753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65376</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>55080</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75755</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>56975</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46145</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>66168</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>47214</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>66753</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,46%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65376</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>55415</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>75967</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108925</t>
+          <t>108071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137386</t>
+          <t>137349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156253</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>116071</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>105874</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>125746</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>58,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>69,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>110014</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>100342</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>121531</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>98893</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>119779</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>64,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>58,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>70,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>116071</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>105471</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>126590</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>64,5%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210780</t>
+          <t>213204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240168</t>
+          <t>241353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>63884</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>54209</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>74081</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>41,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>61323</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>49806</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>70995</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>51558</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>72444</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>35,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>29,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>41,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>63884</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>53365</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>74484</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>35,5%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111124</t>
+          <t>109939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140512</t>
+          <t>138088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>465303</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>444098</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>487265</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>61,86%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>455948</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>433746</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>477138</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>436076</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>477724</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>465303</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>444078</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>487362</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>890450</t>
+          <t>890344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>953410</t>
+          <t>952094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,19%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>286922</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>264960</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>308127</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,14%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>361</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>252344</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>231154</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>274546</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>230568</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>272216</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>286922</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>264863</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>308147</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>507107</t>
+          <t>508423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570067</t>
+          <t>570173</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>68330</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>59039</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>77315</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>74761</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65813</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83541</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>65884</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>83220</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>56,79%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>68330</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>59141</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>77112</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,03%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129635</t>
+          <t>131417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155284</t>
+          <t>155629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55834</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46849</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65125</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>56893</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48113</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>65841</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48434</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>65770</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>43,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55834</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47052</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65023</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,97%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100534</t>
+          <t>100189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126183</t>
+          <t>124401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>136635</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124182</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>149740</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>53,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>48,49%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>58,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>100596</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>88051</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>112164</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>89521</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>111982</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>48,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>42,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>53,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>136635</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>122775</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>148933</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>53,36%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219207</t>
+          <t>220318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>254661</t>
+          <t>254510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>119449</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>106344</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>131902</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>41,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>51,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>107852</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>96284</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>120397</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>96466</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>118927</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>51,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>57,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>119449</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>107151</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>133309</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>46,64%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209871</t>
+          <t>210022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>245325</t>
+          <t>244214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>256084</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>208448</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>256084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>94293</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>83053</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>105421</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>99780</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88716</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>111403</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>87775</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>109705</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>53,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>94293</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>83325</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>105210</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,59%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179502</t>
+          <t>179025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209569</t>
+          <t>209769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,11%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92094</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>80966</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>103334</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>55,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>87660</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76037</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>98724</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>77735</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>99665</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>46,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>92094</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>81177</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>103062</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>49,41%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164258</t>
+          <t>164058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194325</t>
+          <t>194802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186387</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>187440</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91243</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80517</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>102150</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>52,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>46,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>58,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>87202</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>76470</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>98232</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>75726</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>97315</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>50,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>56,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>91243</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>80577</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>102749</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>52,63%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162271</t>
+          <t>162296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193877</t>
+          <t>196399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82134</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>71227</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>92860</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>41,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>85436</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>74406</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96168</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>75323</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>96912</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>49,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>55,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82134</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>70628</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>92800</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>47,37%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152138</t>
+          <t>149616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183744</t>
+          <t>183719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173377</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172638</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>367827</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>410849</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>362339</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>340584</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>383439</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>340992</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>383063</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>51,75%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>54,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>390501</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>366690</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>411755</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>722137</t>
+          <t>722197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>784270</t>
+          <t>783510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>349510</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>329162</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>372184</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>517</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>337842</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>316742</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>359597</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>317118</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>359189</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,25%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>45,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>349510</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>328256</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>373321</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>655922</t>
+          <t>656682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>718055</t>
+          <t>717995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31202</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26481</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35948</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33798</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27555</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39023</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>58,77%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37057</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30940</t>
+          <t>25013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70855</t>
+          <t>61534</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63154</t>
+          <t>54261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>68950</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19335</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14589</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24056</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23713</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18488</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29956</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>21759</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30504</t>
+          <t>27077</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>48100</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39530</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55801</t>
+          <t>48366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>104036</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>93946</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>113351</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>96801</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>86057</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>107172</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>60,77%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>54,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>67,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>120031</t>
+          <t>89813</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109306</t>
+          <t>79949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131387</t>
+          <t>98592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>216833</t>
+          <t>193849</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201832</t>
+          <t>181047</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232299</t>
+          <t>206230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,19%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>52869</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43554</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>62959</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>62498</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52127</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73242</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>39,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61816</t>
+          <t>55705</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>46926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72541</t>
+          <t>65569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>124314</t>
+          <t>108574</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108848</t>
+          <t>96193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139315</t>
+          <t>121376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156905</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341147</t>
+          <t>302423</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108861</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95743</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>121950</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>115565</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>104136</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>125461</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>59,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>111383</t>
+          <t>116071</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96240</t>
+          <t>103161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125285</t>
+          <t>125761</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>226947</t>
+          <t>224931</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207092</t>
+          <t>208536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>245684</t>
+          <t>241346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,41%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>90308</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>77219</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>103426</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>38,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>58323</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48427</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>69752</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>33,54%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100164</t>
+          <t>59447</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86262</t>
+          <t>49757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115307</t>
+          <t>72357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>158487</t>
+          <t>149755</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139750</t>
+          <t>133340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178342</t>
+          <t>166150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>176046</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>152518</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>192807</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>60,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>65,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>169743</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>150693</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>201725</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>61,85%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>54,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>177218</t>
+          <t>156006</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151679</t>
+          <t>141538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195979</t>
+          <t>170265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>346961</t>
+          <t>332052</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>318152</t>
+          <t>306596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389379</t>
+          <t>356800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>116599</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>99838</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>140127</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>34,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>47,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>104715</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72733</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>123765</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38,15%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>45,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>128265</t>
+          <t>99472</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109504</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153804</t>
+          <t>113940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>232980</t>
+          <t>216070</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190562</t>
+          <t>191322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261789</t>
+          <t>241526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274458</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579941</t>
+          <t>548122</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>420145</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>393508</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>445390</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>63,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>415906</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>391941</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>454634</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>62,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>445689</t>
+          <t>392221</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>411370</t>
+          <t>372390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>473302</t>
+          <t>411409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>861595</t>
+          <t>812366</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>822563</t>
+          <t>779070</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>903394</t>
+          <t>843161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>279111</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>253866</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>305748</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>353</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>249250</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>210522</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>273215</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>37,47%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>314633</t>
+          <t>236382</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>287020</t>
+          <t>217194</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348952</t>
+          <t>256213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>563882</t>
+          <t>515493</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>522083</t>
+          <t>484698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>602914</t>
+          <t>548789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
